--- a/config/gem/suit.xlsx
+++ b/config/gem/suit.xlsx
@@ -1232,7 +1232,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>シールド防御</t>
+          <t>盾牌防御</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>シールド防御</t>
+          <t>盾牌防御</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>シールド防御</t>
+          <t>盾牌防御</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>シールド防御</t>
+          <t>盾牌防御</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>シールド防御</t>
+          <t>盾牌防御</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>シールド防御</t>
+          <t>盾牌防御</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>シールド防御</t>
+          <t>盾牌防御</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>シールド防御</t>
+          <t>盾牌防御</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>シールド防御</t>
+          <t>盾牌防御</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>シールド防御</t>
+          <t>盾牌防御</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>金剛</t>
+          <t>金刚</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>金剛</t>
+          <t>金刚</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>金剛</t>
+          <t>金刚</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>金剛</t>
+          <t>金刚</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>金剛</t>
+          <t>金刚</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>金剛</t>
+          <t>金刚</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>金剛</t>
+          <t>金刚</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>金剛</t>
+          <t>金刚</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>金剛</t>
+          <t>金刚</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>金剛</t>
+          <t>金刚</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>庇護</t>
+          <t>庇护</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>庇護</t>
+          <t>庇护</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>庇護</t>
+          <t>庇护</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>庇護</t>
+          <t>庇护</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>庇護</t>
+          <t>庇护</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>閃光</t>
+          <t>闪光</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>閃光</t>
+          <t>闪光</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>閃光</t>
+          <t>闪光</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>閃光</t>
+          <t>闪光</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>閃光</t>
+          <t>闪光</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>報復</t>
+          <t>报复</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>報復</t>
+          <t>报复</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>報復</t>
+          <t>报复</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>報復</t>
+          <t>报复</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>報復</t>
+          <t>报复</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
